--- a/suddivisione lavoro.xlsx
+++ b/suddivisione lavoro.xlsx
@@ -1,30 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47DFC983-9140-438C-AB3D-A421C218B4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\W0rdle\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B7F0DB-0434-477D-B554-7690456CC284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -109,7 +103,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,7 +194,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -497,12 +491,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:D22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
@@ -512,7 +506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -522,7 +516,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>4</v>
@@ -532,7 +526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -542,7 +536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>6</v>
@@ -552,7 +546,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>7</v>
@@ -562,7 +556,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>8</v>
@@ -572,7 +566,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>9</v>
@@ -584,7 +578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -596,7 +590,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -606,7 +600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>13</v>
@@ -616,7 +610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>14</v>
@@ -626,7 +620,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>15</v>
@@ -636,7 +630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
         <v>16</v>
@@ -646,7 +640,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>17</v>
@@ -656,17 +650,17 @@
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -676,7 +670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>20</v>
@@ -686,7 +680,7 @@
       </c>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>21</v>
@@ -696,7 +690,7 @@
       </c>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>22</v>
@@ -706,7 +700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
         <v>23</v>
